--- a/data/trans_dic/IP2005-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen los dientes sanos</t>
+          <t>Menores que tienen los dientes sanos (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,98; 96,62</t>
+          <t>87,86; 96,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,94; 96,86</t>
+          <t>87,0; 96,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,94; 98,36</t>
+          <t>87,72; 98,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77,3; 89,06</t>
+          <t>77,66; 89,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,0; 94,93</t>
+          <t>85,06; 95,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,34; 98,22</t>
+          <t>89,54; 97,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,48; 96,01</t>
+          <t>85,98; 95,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83,97; 93,54</t>
+          <t>84,05; 93,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88,3; 94,7</t>
+          <t>88,36; 94,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90,35; 96,7</t>
+          <t>90,74; 96,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89,36; 96,03</t>
+          <t>89,24; 96,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,7; 90,42</t>
+          <t>82,95; 90,29</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,57; 95,98</t>
+          <t>85,06; 95,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,89; 96,08</t>
+          <t>85,85; 96,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,31; 97,92</t>
+          <t>90,83; 98,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78,0; 90,33</t>
+          <t>77,71; 89,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,73; 95,01</t>
+          <t>84,57; 94,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,31; 98,63</t>
+          <t>92,32; 98,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,49; 96,45</t>
+          <t>87,41; 96,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>80,08; 92,95</t>
+          <t>79,75; 92,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,4; 94,44</t>
+          <t>87,12; 94,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91,48; 96,93</t>
+          <t>91,13; 96,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90,53; 96,35</t>
+          <t>90,67; 96,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,41; 89,86</t>
+          <t>81,7; 89,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,57; 94,62</t>
+          <t>81,65; 94,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,08; 93,04</t>
+          <t>80,46; 92,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,7; 97,94</t>
+          <t>86,73; 97,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82,53; 95,87</t>
+          <t>82,55; 96,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,35; 94,49</t>
+          <t>84,4; 94,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,48; 95,68</t>
+          <t>85,19; 95,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,48; 97,26</t>
+          <t>88,28; 97,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77,46; 93,8</t>
+          <t>77,79; 94,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85,65; 93,65</t>
+          <t>85,8; 93,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,74; 93,18</t>
+          <t>85,47; 93,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,96; 97,25</t>
+          <t>90,3; 96,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82,05; 93,34</t>
+          <t>82,37; 93,35</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,47; 90,79</t>
+          <t>83,04; 90,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,83; 93,15</t>
+          <t>86,0; 93,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,22; 94,0</t>
+          <t>87,34; 93,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,99; 93,63</t>
+          <t>85,12; 94,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,69; 91,5</t>
+          <t>83,67; 91,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,26; 95,46</t>
+          <t>89,56; 95,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,92; 91,4</t>
+          <t>83,34; 91,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>81,28; 90,0</t>
+          <t>81,77; 90,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,99; 90,33</t>
+          <t>84,4; 89,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89,03; 93,89</t>
+          <t>89,16; 93,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86,67; 91,92</t>
+          <t>86,82; 91,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,63; 91,22</t>
+          <t>84,62; 90,85</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,0; 92,91</t>
+          <t>82,91; 93,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,48; 91,69</t>
+          <t>81,81; 91,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,84; 96,18</t>
+          <t>88,82; 96,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81,88; 92,21</t>
+          <t>82,28; 92,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,0; 91,58</t>
+          <t>82,54; 91,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,17; 90,2</t>
+          <t>79,88; 90,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,96; 93,64</t>
+          <t>84,78; 93,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,97; 94,33</t>
+          <t>85,11; 95,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>84,4; 91,3</t>
+          <t>84,44; 91,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82,47; 89,96</t>
+          <t>82,94; 90,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88,47; 94,08</t>
+          <t>88,24; 94,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,44; 92,91</t>
+          <t>86,01; 92,65</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,21; 98,12</t>
+          <t>89,2; 98,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,94; 100,0</t>
+          <t>91,87; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,47; 97,54</t>
+          <t>86,12; 97,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82,67; 95,89</t>
+          <t>83,62; 95,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>90,49; 98,94</t>
+          <t>89,62; 98,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80,16; 93,23</t>
+          <t>79,34; 93,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,29; 98,97</t>
+          <t>90,0; 98,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78,8; 93,92</t>
+          <t>79,03; 94,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91,03; 97,54</t>
+          <t>91,62; 97,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>86,89; 95,02</t>
+          <t>87,04; 95,1</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>90,52; 97,35</t>
+          <t>89,77; 97,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>83,62; 93,82</t>
+          <t>84,22; 93,74</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,11; 92,08</t>
+          <t>88,0; 91,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>88,31; 92,34</t>
+          <t>88,22; 92,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91,41; 94,58</t>
+          <t>91,19; 94,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85,57; 90,28</t>
+          <t>85,24; 89,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,82; 91,64</t>
+          <t>87,7; 91,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,81; 93,29</t>
+          <t>89,85; 93,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,17; 93,01</t>
+          <t>89,04; 92,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>85,98; 90,54</t>
+          <t>86,01; 90,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>88,68; 91,3</t>
+          <t>88,79; 91,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89,46; 92,24</t>
+          <t>89,71; 92,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90,86; 93,47</t>
+          <t>90,7; 93,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,46; 89,67</t>
+          <t>86,56; 89,75</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen los dientes sanos (tasa de respuesta: 99,37%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>88431</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>77550</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>73427</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86592</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82690</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78582</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>82762</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>121135</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>171122</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>156132</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>156190</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>207727</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>83453; 91805</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>72497; 80643</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67770; 75826</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80188; 92364</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>77410; 86458</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>73997; 80770</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>77510; 86216</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>113811; 126192</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>164348; 175859</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>150607; 160766</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>149384; 160847</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>197980; 215487</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>73746</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>78715</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>92446</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>80145</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>74882</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88868</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98019</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>81220</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>148627</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>167583</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>190465</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>161365</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>68368; 76581</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>73199; 82262</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>88158; 95132</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>73578; 85198</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>69672; 78088</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>85005; 90821</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>92244; 101753</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>74361; 85956</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>141808; 153782</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>161606; 171976</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>183677; 194979</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>153531; 168438</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>57058</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71416</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>55121</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45239</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88439</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75543</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>65956</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>55395</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>145497</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>146958</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>121077</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>100634</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>52160; 60488</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>65371; 75453</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>50728; 57178</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>41214; 48053</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>82565; 92411</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>70080; 78773</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>61891; 68679</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>49117; 59536</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>138746; 151113</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>139754; 152591</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>116121; 124695</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>93134; 105540</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>166329</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>171544</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>187669</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>191808</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>163241</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>195520</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>178224</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>183782</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>329570</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>367063</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>365893</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>375590</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>157932; 172988</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>163699; 177742</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>180118; 193423</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>182121; 201227</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>155308; 169687</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>188632; 200720</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>168709; 185058</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>173842; 192665</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>317178; 337981</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>357515; 375972</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>354800; 375714</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>360944; 387539</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>86080</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>120009</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122022</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>103427</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>104878</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>110871</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>120877</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>145044</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>190957</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>230879</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>242899</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>248471</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>80280; 90444</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>112380; 125673</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>116166; 125728</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>96920; 108661</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>98807; 109949</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>102970; 116457</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>113978; 125891</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>135778; 151676</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>182841; 197572</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>220857; 240562</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>234053; 249476</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>238541; 256947</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>66992</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>48583</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>52848</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>62569</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>62359</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>59044</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>62486</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>62331</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>129350</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>107627</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>115334</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>124900</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>63108; 69430</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>45844; 49899</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48812; 55307</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57608; 65815</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>58326; 64404</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>53551; 62915</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>58511; 64341</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>55681; 66361</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>124444; 132635</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>102178; 111651</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>109240; 118482</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>117362; 130619</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1669</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1693</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1749</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1610</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>538637</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>567817</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>583533</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>569778</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>576488</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>608426</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>608323</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>648908</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1115124</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1176243</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1191856</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1218688</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>525365; 548793</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>553550; 579708</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>571292; 593065</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>552801; 583490</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>562666; 587800</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>596588; 619023</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>594507; 620705</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>631644; 663992</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1099831; 1132830</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1158544; 1193852</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1173875; 1207586</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1197054; 1241161</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2005-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,86; 96,66</t>
+          <t>88,0; 96,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,0; 96,77</t>
+          <t>87,07; 96,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,72; 98,15</t>
+          <t>89,0; 98,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77,66; 89,45</t>
+          <t>77,14; 89,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,06; 95,0</t>
+          <t>84,99; 95,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,54; 97,74</t>
+          <t>89,62; 98,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,98; 95,64</t>
+          <t>85,58; 95,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>84,05; 93,19</t>
+          <t>84,04; 93,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88,36; 94,55</t>
+          <t>88,04; 94,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90,74; 96,86</t>
+          <t>90,7; 96,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89,24; 96,08</t>
+          <t>89,4; 96,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,95; 90,29</t>
+          <t>82,64; 90,23</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,06; 95,27</t>
+          <t>85,02; 95,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,85; 96,47</t>
+          <t>86,38; 96,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,83; 98,02</t>
+          <t>90,4; 97,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,71; 89,98</t>
+          <t>77,41; 90,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,57; 94,78</t>
+          <t>84,45; 95,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,32; 98,64</t>
+          <t>92,3; 98,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,41; 96,42</t>
+          <t>87,56; 96,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>79,75; 92,18</t>
+          <t>80,41; 92,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,12; 94,48</t>
+          <t>86,96; 94,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91,13; 96,97</t>
+          <t>91,4; 97,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90,67; 96,25</t>
+          <t>90,73; 96,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,7; 89,63</t>
+          <t>81,34; 89,82</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,65; 94,68</t>
+          <t>81,1; 94,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,46; 92,87</t>
+          <t>80,56; 92,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,73; 97,75</t>
+          <t>86,71; 97,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82,55; 96,25</t>
+          <t>82,76; 96,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,4; 94,47</t>
+          <t>84,92; 94,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,19; 95,76</t>
+          <t>85,78; 95,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,28; 97,96</t>
+          <t>88,66; 97,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77,79; 94,3</t>
+          <t>77,64; 94,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85,8; 93,45</t>
+          <t>85,32; 93,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,47; 93,32</t>
+          <t>85,11; 93,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90,3; 96,96</t>
+          <t>89,92; 96,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82,37; 93,35</t>
+          <t>83,06; 93,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,04; 90,96</t>
+          <t>83,2; 90,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,0; 93,38</t>
+          <t>85,77; 93,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,34; 93,79</t>
+          <t>87,29; 93,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,12; 94,05</t>
+          <t>85,33; 93,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,67; 91,42</t>
+          <t>83,95; 91,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,56; 95,3</t>
+          <t>89,38; 95,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,34; 91,42</t>
+          <t>83,71; 91,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>81,77; 90,62</t>
+          <t>81,6; 90,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,4; 89,94</t>
+          <t>84,64; 90,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89,16; 93,77</t>
+          <t>89,07; 93,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86,82; 91,94</t>
+          <t>86,9; 91,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,62; 90,85</t>
+          <t>85,02; 91,19</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,91; 93,41</t>
+          <t>83,02; 93,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>81,81; 91,48</t>
+          <t>81,57; 91,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,82; 96,13</t>
+          <t>88,88; 96,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,28; 92,25</t>
+          <t>81,95; 92,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,54; 91,85</t>
+          <t>82,58; 92,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,88; 90,35</t>
+          <t>80,4; 90,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,78; 93,64</t>
+          <t>84,68; 93,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,11; 95,07</t>
+          <t>85,36; 94,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>84,44; 91,25</t>
+          <t>84,43; 91,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82,94; 90,34</t>
+          <t>83,06; 89,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88,24; 94,06</t>
+          <t>88,5; 94,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,01; 92,65</t>
+          <t>85,82; 92,44</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,2; 98,13</t>
+          <t>89,46; 98,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,87; 100,0</t>
+          <t>92,01; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,12; 97,59</t>
+          <t>86,61; 97,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83,62; 95,53</t>
+          <t>82,56; 95,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>89,62; 98,96</t>
+          <t>90,15; 98,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79,34; 93,21</t>
+          <t>80,16; 92,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,0; 98,97</t>
+          <t>89,61; 98,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>79,03; 94,19</t>
+          <t>79,77; 94,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91,62; 97,65</t>
+          <t>91,55; 97,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87,04; 95,1</t>
+          <t>86,75; 95,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89,77; 97,36</t>
+          <t>90,44; 97,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>84,22; 93,74</t>
+          <t>84,16; 93,61</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,0; 91,92</t>
+          <t>88,33; 91,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>88,22; 92,39</t>
+          <t>88,37; 92,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91,19; 94,66</t>
+          <t>91,22; 94,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85,24; 89,97</t>
+          <t>85,34; 90,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,7; 91,61</t>
+          <t>87,99; 91,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,85; 93,23</t>
+          <t>89,65; 93,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,04; 92,97</t>
+          <t>89,08; 92,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>86,01; 90,41</t>
+          <t>85,81; 90,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>88,79; 91,46</t>
+          <t>88,6; 91,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89,71; 92,44</t>
+          <t>89,6; 92,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90,7; 93,31</t>
+          <t>90,69; 93,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,56; 89,75</t>
+          <t>86,52; 89,88</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>83453; 91805</t>
+          <t>83585; 91593</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72497; 80643</t>
+          <t>72562; 80504</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67770; 75826</t>
+          <t>68754; 75976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80188; 92364</t>
+          <t>79652; 92062</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77410; 86458</t>
+          <t>77354; 86486</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73997; 80770</t>
+          <t>74064; 81238</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77510; 86216</t>
+          <t>77147; 86516</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>113811; 126192</t>
+          <t>113802; 126018</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>164348; 175859</t>
+          <t>163744; 176181</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>150607; 160766</t>
+          <t>150532; 160204</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>149384; 160847</t>
+          <t>149649; 160739</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>197980; 215487</t>
+          <t>197242; 215363</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68368; 76581</t>
+          <t>68339; 76953</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73199; 82262</t>
+          <t>73652; 82467</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88158; 95132</t>
+          <t>87741; 95042</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73578; 85198</t>
+          <t>73295; 85290</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69672; 78088</t>
+          <t>69577; 78311</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85005; 90821</t>
+          <t>84985; 90804</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92244; 101753</t>
+          <t>92394; 101740</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74361; 85956</t>
+          <t>74981; 86060</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>141808; 153782</t>
+          <t>141543; 153058</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>161606; 171976</t>
+          <t>162093; 172143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>183677; 194979</t>
+          <t>183795; 195422</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>153531; 168438</t>
+          <t>152864; 168795</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>52160; 60488</t>
+          <t>51811; 60352</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65371; 75453</t>
+          <t>65451; 75375</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50728; 57178</t>
+          <t>50721; 57215</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41214; 48053</t>
+          <t>41317; 47928</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82565; 92411</t>
+          <t>83070; 92452</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70080; 78773</t>
+          <t>70565; 78845</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61891; 68679</t>
+          <t>62161; 68635</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49117; 59536</t>
+          <t>49018; 59550</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>138746; 151113</t>
+          <t>137974; 151228</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>139754; 152591</t>
+          <t>139155; 152238</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116121; 124695</t>
+          <t>115639; 124660</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93134; 105540</t>
+          <t>93913; 105636</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>157932; 172988</t>
+          <t>158238; 172959</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>163699; 177742</t>
+          <t>163258; 177380</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>180118; 193423</t>
+          <t>180028; 193671</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>182121; 201227</t>
+          <t>182583; 200639</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>155308; 169687</t>
+          <t>155816; 169972</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>188632; 200720</t>
+          <t>188260; 200783</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>168709; 185058</t>
+          <t>169462; 184662</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>173842; 192665</t>
+          <t>173483; 192186</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>317178; 337981</t>
+          <t>318087; 338619</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>357515; 375972</t>
+          <t>357140; 375274</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>354800; 375714</t>
+          <t>355117; 375644</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>360944; 387539</t>
+          <t>362654; 388990</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>80280; 90444</t>
+          <t>80388; 90139</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>112380; 125673</t>
+          <t>112049; 125919</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>116166; 125728</t>
+          <t>116247; 125895</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96920; 108661</t>
+          <t>96530; 108730</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98807; 109949</t>
+          <t>98857; 110203</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>102970; 116457</t>
+          <t>103640; 116608</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>113978; 125891</t>
+          <t>113845; 125528</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>135778; 151676</t>
+          <t>136185; 151056</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182841; 197572</t>
+          <t>182813; 197350</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>220857; 240562</t>
+          <t>221165; 239287</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>234053; 249476</t>
+          <t>234725; 249313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>238541; 256947</t>
+          <t>237997; 256355</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>63108; 69430</t>
+          <t>63293; 69425</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45844; 49899</t>
+          <t>45912; 49899</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48812; 55307</t>
+          <t>49089; 55379</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57608; 65815</t>
+          <t>56877; 65941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58326; 64404</t>
+          <t>58670; 64390</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53551; 62915</t>
+          <t>54109; 62615</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58511; 64341</t>
+          <t>58259; 64340</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>55681; 66361</t>
+          <t>56203; 66439</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>124444; 132635</t>
+          <t>124353; 132642</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102178; 111651</t>
+          <t>101837; 111877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>109240; 118482</t>
+          <t>110057; 118452</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>117362; 130619</t>
+          <t>117281; 130449</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>525365; 548793</t>
+          <t>527312; 549008</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>553550; 579708</t>
+          <t>554486; 579540</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>571292; 593065</t>
+          <t>571491; 592735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>552801; 583490</t>
+          <t>553416; 583996</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>562666; 587800</t>
+          <t>564588; 588649</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>596588; 619023</t>
+          <t>595241; 619802</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>594507; 620705</t>
+          <t>594794; 620061</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>631644; 663992</t>
+          <t>630183; 663054</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1099831; 1132830</t>
+          <t>1097409; 1131526</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1158544; 1193852</t>
+          <t>1157177; 1190749</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1173875; 1207586</t>
+          <t>1173638; 1205787</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1197054; 1241161</t>
+          <t>1196503; 1242960</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2005-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>90,86%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91,81%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>93,1%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>93,06%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>95,05%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>83,86%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>90,86%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>88,0; 96,43</t>
+          <t>85,0; 94,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,07; 96,61</t>
+          <t>89,34; 98,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,0; 98,35</t>
+          <t>85,48; 96,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77,14; 89,16</t>
+          <t>83,04; 93,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,99; 95,03</t>
+          <t>87,98; 96,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,62; 98,3</t>
+          <t>86,94; 96,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,58; 95,97</t>
+          <t>88,94; 98,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>84,04; 93,06</t>
+          <t>77,13; 89,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88,04; 94,72</t>
+          <t>88,3; 94,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90,7; 96,52</t>
+          <t>90,35; 96,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89,4; 96,02</t>
+          <t>89,36; 96,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,64; 90,23</t>
+          <t>82,28; 90,28</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>90,89%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>96,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>92,88%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>87,4%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>91,75%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>92,31%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>95,25%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>84,65%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>90,89%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>96,52%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,02; 95,74</t>
+          <t>84,73; 95,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,38; 96,71</t>
+          <t>92,31; 98,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,4; 97,93</t>
+          <t>87,49; 96,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,41; 90,08</t>
+          <t>80,19; 92,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,45; 95,05</t>
+          <t>85,57; 95,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,3; 98,62</t>
+          <t>85,89; 96,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,56; 96,41</t>
+          <t>90,31; 97,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>80,41; 92,29</t>
+          <t>78,04; 90,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,96; 94,04</t>
+          <t>87,4; 94,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91,4; 97,07</t>
+          <t>91,48; 96,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90,73; 96,47</t>
+          <t>90,53; 96,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,34; 89,82</t>
+          <t>81,42; 90,07</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>90,41%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91,83%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>94,08%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>89,32%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>87,9%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>94,24%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>90,61%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>90,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,1; 94,47</t>
+          <t>84,35; 94,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,56; 92,77</t>
+          <t>85,48; 95,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,71; 97,82</t>
+          <t>88,48; 97,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82,76; 96,0</t>
+          <t>78,0; 93,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,92; 94,51</t>
+          <t>82,57; 94,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,78; 95,85</t>
+          <t>81,08; 93,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,66; 97,9</t>
+          <t>87,7; 97,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77,64; 94,32</t>
+          <t>83,7; 96,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85,32; 93,52</t>
+          <t>85,65; 93,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,11; 93,11</t>
+          <t>85,74; 93,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,92; 96,94</t>
+          <t>89,96; 97,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83,06; 93,43</t>
+          <t>83,28; 93,75</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87,95%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>88,04%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>85,9%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>87,46%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>90,12%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>91,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>87,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>92,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>88,04%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,2; 90,94</t>
+          <t>83,69; 91,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,77; 93,19</t>
+          <t>89,26; 95,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,29; 93,91</t>
+          <t>83,92; 91,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,33; 93,77</t>
+          <t>80,52; 89,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,95; 91,57</t>
+          <t>83,47; 90,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,38; 95,33</t>
+          <t>85,83; 93,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,71; 91,22</t>
+          <t>87,22; 94,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>81,6; 90,4</t>
+          <t>82,47; 91,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,64; 90,11</t>
+          <t>84,99; 90,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89,07; 93,59</t>
+          <t>89,03; 93,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86,9; 91,92</t>
+          <t>86,67; 91,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,02; 91,19</t>
+          <t>82,97; 89,45</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>87,61%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>90,96%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>88,9%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>87,36%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>93,29%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>87,81%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>87,61%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>89,91%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,02; 93,09</t>
+          <t>82,0; 91,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>81,57; 91,66</t>
+          <t>80,17; 90,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,88; 96,25</t>
+          <t>84,96; 93,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81,95; 92,31</t>
+          <t>84,87; 94,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,58; 92,06</t>
+          <t>83,0; 92,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,4; 90,46</t>
+          <t>82,48; 91,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,68; 93,37</t>
+          <t>88,84; 96,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,36; 94,68</t>
+          <t>81,47; 91,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>84,43; 91,14</t>
+          <t>84,4; 91,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83,06; 89,87</t>
+          <t>82,47; 89,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88,5; 94,0</t>
+          <t>88,47; 94,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,82; 92,44</t>
+          <t>85,34; 92,76</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>95,82%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>87,47%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>89,3%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>94,69%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>97,36%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>93,25%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>90,82%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>95,82%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,46; 98,13</t>
+          <t>90,49; 98,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92,01; 100,0</t>
+          <t>80,16; 93,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,61; 97,71</t>
+          <t>89,29; 98,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82,56; 95,71</t>
+          <t>80,38; 94,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>90,15; 98,94</t>
+          <t>89,21; 98,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80,16; 92,76</t>
+          <t>90,94; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,61; 98,96</t>
+          <t>86,47; 97,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>79,77; 94,3</t>
+          <t>82,97; 96,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91,55; 97,65</t>
+          <t>91,03; 97,54</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>86,75; 95,3</t>
+          <t>86,89; 95,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>90,44; 97,34</t>
+          <t>90,52; 97,35</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>84,16; 93,61</t>
+          <t>84,56; 93,94</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>89,85%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>91,63%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>91,11%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>88,32%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>90,22%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>90,49%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>93,14%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>89,85%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,11%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,33; 91,96</t>
+          <t>87,82; 91,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>88,37; 92,36</t>
+          <t>89,81; 93,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91,22; 94,61</t>
+          <t>89,17; 93,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85,34; 90,05</t>
+          <t>85,95; 90,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,99; 91,74</t>
+          <t>88,11; 92,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,65; 93,34</t>
+          <t>88,31; 92,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,08; 92,87</t>
+          <t>91,41; 94,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>85,81; 90,29</t>
+          <t>84,74; 89,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>88,6; 91,35</t>
+          <t>88,68; 91,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89,6; 92,2</t>
+          <t>89,46; 92,24</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90,69; 93,17</t>
+          <t>90,86; 93,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,52; 89,88</t>
+          <t>86,04; 89,3</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>128</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82690</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>78582</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>82762</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>108249</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>88431</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>77550</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>73427</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>86592</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>82690</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>78582</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82762</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>121135</t>
+          <t>85358</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>207727</t>
+          <t>193607</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>83585; 91593</t>
+          <t>77363; 86398</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72562; 80504</t>
+          <t>73828; 81167</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68754; 75976</t>
+          <t>77058; 86547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79652; 92062</t>
+          <t>100737; 113141</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77354; 86486</t>
+          <t>83562; 91773</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74064; 81238</t>
+          <t>72447; 80714</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77147; 86516</t>
+          <t>68711; 75990</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>113802; 126018</t>
+          <t>78584; 90809</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>163744; 176181</t>
+          <t>164240; 176145</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>150532; 160204</t>
+          <t>149955; 160497</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>149649; 160739</t>
+          <t>149595; 160762</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>197242; 215363</t>
+          <t>183638; 201509</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>119</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>74882</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88868</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>98019</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78270</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>73746</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>78715</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>92446</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>80145</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>74882</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88868</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98019</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>81220</t>
+          <t>81800</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>161365</t>
+          <t>160069</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68339; 76953</t>
+          <t>69805; 78271</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73652; 82467</t>
+          <t>84991; 90814</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87741; 95042</t>
+          <t>92327; 101780</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73295; 85290</t>
+          <t>71811; 83127</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69577; 78311</t>
+          <t>68784; 77153</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84985; 90804</t>
+          <t>73239; 81925</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92394; 101740</t>
+          <t>87653; 95037</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74981; 86060</t>
+          <t>75340; 87211</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>141543; 153058</t>
+          <t>142253; 153715</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>162093; 172143</t>
+          <t>162227; 171900</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>183795; 195422</t>
+          <t>183389; 195184</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>152864; 168795</t>
+          <t>151514; 167621</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>88439</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75543</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65956</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>49804</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>57058</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>71416</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>55121</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>45239</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88439</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75543</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>65956</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55395</t>
+          <t>47119</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100634</t>
+          <t>96923</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51811; 60352</t>
+          <t>82515; 92434</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65451; 75375</t>
+          <t>70313; 78704</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50721; 57215</t>
+          <t>62030; 68186</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41317; 47928</t>
+          <t>44024; 53042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83070; 92452</t>
+          <t>52747; 60447</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70565; 78845</t>
+          <t>65876; 75591</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62161; 68635</t>
+          <t>51296; 57284</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49018; 59550</t>
+          <t>43121; 49653</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>137974; 151228</t>
+          <t>138502; 151443</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>139155; 152238</t>
+          <t>140196; 152359</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115639; 124660</t>
+          <t>115690; 125063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93913; 105636</t>
+          <t>89915; 101216</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>249</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>238</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>163241</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>195520</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>178224</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>169521</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>166329</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>171544</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>187669</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>191808</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>163241</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>195520</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>178224</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>183782</t>
+          <t>153642</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>375590</t>
+          <t>323163</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>158238; 172959</t>
+          <t>155337; 169840</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>163258; 177380</t>
+          <t>187992; 201058</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>180028; 193671</t>
+          <t>169880; 185024</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>182583; 200639</t>
+          <t>158899; 176955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>155816; 169972</t>
+          <t>158746; 172663</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>188260; 200783</t>
+          <t>163377; 177315</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>169462; 184662</t>
+          <t>179874; 193858</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>173483; 192186</t>
+          <t>144746; 159964</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>318087; 338619</t>
+          <t>319391; 339459</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>357140; 375274</t>
+          <t>356979; 376454</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>355117; 375644</t>
+          <t>354179; 375659</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>362654; 388990</t>
+          <t>309341; 333497</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>173</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>183</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>156</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>104878</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>110871</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>120877</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>132568</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>86080</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>120009</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>122022</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>103427</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>104878</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>110871</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>120877</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>145044</t>
+          <t>102885</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>248471</t>
+          <t>235453</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>80388; 90139</t>
+          <t>98152; 109626</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>112049; 125919</t>
+          <t>103342; 116267</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>116247; 125895</t>
+          <t>114216; 125892</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96530; 108730</t>
+          <t>123688; 137620</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98857; 110203</t>
+          <t>80369; 89959</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>103640; 116608</t>
+          <t>113311; 125955</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>113845; 125528</t>
+          <t>116203; 125802</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>136185; 151056</t>
+          <t>95634; 107902</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182813; 197350</t>
+          <t>182754; 197685</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>221165; 239287</t>
+          <t>219592; 239544</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>234725; 249313</t>
+          <t>234647; 249543</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>237997; 256355</t>
+          <t>224549; 244063</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>90</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>62359</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59044</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>62486</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>59891</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>66992</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>48583</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>52848</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>62569</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>62359</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>59044</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>62486</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>62331</t>
+          <t>63994</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>124900</t>
+          <t>123885</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>63293; 69425</t>
+          <t>58894; 64393</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45912; 49899</t>
+          <t>54110; 62930</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49089; 55379</t>
+          <t>58052; 64343</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56877; 65941</t>
+          <t>53908; 63394</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58670; 64390</t>
+          <t>63114; 69418</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54109; 62615</t>
+          <t>45377; 49899</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58259; 64340</t>
+          <t>49010; 55283</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>56203; 66439</t>
+          <t>58377; 67697</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>124353; 132642</t>
+          <t>123651; 132486</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>101837; 111877</t>
+          <t>102007; 111555</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110057; 118452</t>
+          <t>110153; 118467</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>117281; 130449</t>
+          <t>116209; 129087</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>801</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>821</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>877</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>793</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>817</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>576488</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>608426</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>608323</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>598303</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>538637</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>567817</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>583533</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>569778</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>576488</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>608426</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>608323</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>648908</t>
+          <t>534799</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1218688</t>
+          <t>1133101</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>527312; 549008</t>
+          <t>563479; 587979</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>554486; 579540</t>
+          <t>596331; 619454</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>571491; 592735</t>
+          <t>595351; 620988</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>553416; 583996</t>
+          <t>582242; 613002</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>564588; 588649</t>
+          <t>525993; 549726</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>595241; 619802</t>
+          <t>554107; 579385</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>594794; 620061</t>
+          <t>572714; 592540</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>630183; 663054</t>
+          <t>519629; 548368</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1097409; 1131526</t>
+          <t>1098393; 1130871</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1157177; 1190749</t>
+          <t>1155336; 1191276</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1173638; 1205787</t>
+          <t>1175914; 1209660</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1196503; 1242960</t>
+          <t>1110433; 1152530</t>
         </is>
       </c>
     </row>
